--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
-      </c>
-      <c r="E7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45107</v>
       </c>
       <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="H7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -718,42 +726,48 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
@@ -767,22 +781,28 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
@@ -796,8 +816,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,22 +835,24 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
+      <c r="E12" s="3">
+        <v>33200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2800</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -838,8 +866,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,66 +901,84 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,37 +987,45 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4500</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E17" s="3">
-        <v>15900</v>
+        <v>99700</v>
       </c>
       <c r="F17" s="3">
-        <v>11800</v>
+        <v>20100</v>
       </c>
       <c r="G17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>7500</v>
-      </c>
-      <c r="I17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -973,28 +1033,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-15900</v>
+        <v>-98900</v>
       </c>
       <c r="F18" s="3">
-        <v>-11800</v>
+        <v>-16000</v>
       </c>
       <c r="G18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="I18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1072,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1015,28 +1083,34 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>4600</v>
+        <v>-225900</v>
       </c>
       <c r="F20" s="3">
-        <v>3600</v>
+        <v>-2800</v>
       </c>
       <c r="G20" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1044,115 +1118,139 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-11300</v>
+        <v>-324800</v>
       </c>
       <c r="F21" s="3">
-        <v>-8200</v>
+        <v>-18700</v>
       </c>
       <c r="G21" s="3">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>39400</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-1000</v>
+      <c r="D23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E23" s="3">
-        <v>-11300</v>
+        <v>-327600</v>
       </c>
       <c r="F23" s="3">
-        <v>-8200</v>
+        <v>-58200</v>
       </c>
       <c r="G23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="I23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>900</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>600</v>
-      </c>
-      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-1900</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E26" s="3">
-        <v>-12200</v>
+        <v>-327600</v>
       </c>
       <c r="F26" s="3">
-        <v>-9100</v>
+        <v>-58200</v>
       </c>
       <c r="G26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-1900</v>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E27" s="3">
-        <v>-12200</v>
+        <v>-327600</v>
       </c>
       <c r="F27" s="3">
-        <v>-9100</v>
+        <v>-58200</v>
       </c>
       <c r="G27" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1488,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1363,57 +1503,69 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-4600</v>
+        <v>225900</v>
       </c>
       <c r="F32" s="3">
-        <v>-3600</v>
+        <v>2800</v>
       </c>
       <c r="G32" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-1900</v>
+      <c r="D33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E33" s="3">
-        <v>-12200</v>
+        <v>-327600</v>
       </c>
       <c r="F33" s="3">
-        <v>-9100</v>
+        <v>-58200</v>
       </c>
       <c r="G33" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-1900</v>
+      <c r="D35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E35" s="3">
-        <v>-12200</v>
+        <v>-327600</v>
       </c>
       <c r="F35" s="3">
-        <v>-9100</v>
+        <v>-58200</v>
       </c>
       <c r="G35" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
-      </c>
-      <c r="E38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45107</v>
       </c>
       <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="H38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1702,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>400</v>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E41" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+        <v>233700</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,37 +1768,49 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,124 +1838,154 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
+        <v>40400</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>400</v>
+      <c r="D46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E46" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F46" s="3">
+        <v>274100</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="L46" s="3">
+        <v>200</v>
+      </c>
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
-        <v>200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>200</v>
-      </c>
-      <c r="K46" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>310600</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>307200</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>307100</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>303500</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>300300</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>297900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>293700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1791,8 +2013,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,22 +2083,28 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -1876,10 +2116,16 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>311000</v>
+      <c r="D54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E54" s="3">
-        <v>310500</v>
-      </c>
-      <c r="F54" s="3">
-        <v>307300</v>
-      </c>
-      <c r="G54" s="3">
-        <v>303800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>300500</v>
-      </c>
-      <c r="I54" s="3">
+        <v>274400</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>298100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>294000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,124 +2222,150 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>6800</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H58" s="3">
+        <v>50200</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>49400</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>48000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>33500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>21500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>11400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>56200</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E60" s="3">
-        <v>53800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>37700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>25500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>23500</v>
-      </c>
-      <c r="I60" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>14800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2107,37 +2393,49 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>10100</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>10100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>10100</v>
+        <v>200</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>10100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>66200</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E66" s="3">
-        <v>63800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>47700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>35600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I66" s="3">
+        <v>64200</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>24900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-63900</v>
+      <c r="D72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E72" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-44200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-32900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="I72" s="3">
+        <v>-2871900</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-24000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-16300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>244800</v>
+      <c r="D76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E76" s="3">
-        <v>246700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>259600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>268300</v>
-      </c>
-      <c r="H76" s="3">
-        <v>267000</v>
-      </c>
-      <c r="I76" s="3">
+        <v>210300</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>273200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>277000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
-      </c>
-      <c r="E80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45107</v>
       </c>
       <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="H80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-1900</v>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E81" s="3">
-        <v>-12200</v>
+        <v>-327600</v>
       </c>
       <c r="F81" s="3">
-        <v>-9100</v>
+        <v>-58200</v>
       </c>
       <c r="G81" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-3400</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>-1100</v>
+        <v>-9300</v>
       </c>
       <c r="F89" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,13 +3287,15 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -2876,8 +3318,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,25 +3388,31 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3">
-        <v>100</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
@@ -2963,8 +3423,14 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3473,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3578,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>500</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
-        <v>800</v>
+        <v>280500</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="G100" s="3">
-        <v>600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>3300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3648,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-2900</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E102" s="3">
-        <v>3200</v>
+        <v>271200</v>
       </c>
       <c r="F102" s="3">
-        <v>-100</v>
+        <v>-7200</v>
       </c>
       <c r="G102" s="3">
-        <v>200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+        <v>-3800</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,95 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
         <v>800</v>
       </c>
       <c r="F8" s="3">
-        <v>4100</v>
+        <v>800</v>
       </c>
       <c r="G8" s="3">
+        <v>800</v>
+      </c>
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="I8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -752,31 +757,34 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>200</v>
-      </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -787,32 +795,35 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>900</v>
       </c>
       <c r="E10" s="3">
+        <v>800</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
-        <v>3900</v>
-      </c>
       <c r="G10" s="3">
+        <v>700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
@@ -822,8 +833,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,32 +851,33 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>3900</v>
       </c>
       <c r="E12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F12" s="3">
         <v>33200</v>
       </c>
-      <c r="F12" s="3">
-        <v>9700</v>
-      </c>
       <c r="G12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J12" s="3">
         <v>2800</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
@@ -872,8 +887,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,22 +925,25 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -933,8 +954,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -942,34 +963,37 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -977,8 +1001,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1016,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>22100</v>
       </c>
       <c r="E17" s="3">
-        <v>99700</v>
+        <v>19500</v>
       </c>
       <c r="F17" s="3">
-        <v>20100</v>
+        <v>99100</v>
       </c>
       <c r="G17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I17" s="3">
         <v>5000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="J17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-21100</v>
       </c>
       <c r="E18" s="3">
-        <v>-98900</v>
+        <v>-18700</v>
       </c>
       <c r="F18" s="3">
-        <v>-16000</v>
+        <v>-98400</v>
       </c>
       <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,104 +1108,111 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>-225900</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>-2800</v>
+        <v>225900</v>
       </c>
       <c r="G20" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-20300</v>
       </c>
       <c r="E21" s="3">
-        <v>-324800</v>
+        <v>-18700</v>
       </c>
       <c r="F21" s="3">
-        <v>-18700</v>
+        <v>-324300</v>
       </c>
       <c r="G21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J21" s="3">
         <v>1800</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>-3500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
         <v>2800</v>
       </c>
-      <c r="F22" s="3">
-        <v>39400</v>
-      </c>
       <c r="G22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1179,54 +1220,60 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-19200</v>
       </c>
       <c r="E23" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-327600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1240,17 +1287,20 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1334,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-19200</v>
       </c>
       <c r="E26" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-327600</v>
       </c>
-      <c r="F26" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-19200</v>
       </c>
       <c r="E27" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-327600</v>
       </c>
-      <c r="F27" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1448,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1486,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1524,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1562,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>225900</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
-        <v>2800</v>
+        <v>-225900</v>
       </c>
       <c r="G32" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-19200</v>
       </c>
       <c r="E33" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-327600</v>
       </c>
-      <c r="F33" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1676,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-19200</v>
       </c>
       <c r="E35" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-327600</v>
       </c>
-      <c r="F35" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1775,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,34 +1791,35 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
+      <c r="D41" s="3">
+        <v>372100</v>
       </c>
       <c r="E41" s="3">
+        <v>344000</v>
+      </c>
+      <c r="F41" s="3">
         <v>233700</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
+      <c r="G41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2400</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -1739,13 +1827,16 @@
       <c r="M41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300700</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1774,34 +1865,37 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>400</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1809,31 +1903,34 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1844,16 +1941,19 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3">
-        <v>40400</v>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -1870,8 +1970,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>200</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
@@ -1879,104 +1979,113 @@
       <c r="M45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>682100</v>
       </c>
       <c r="E46" s="3">
+        <v>353500</v>
+      </c>
+      <c r="F46" s="3">
         <v>274100</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
+      <c r="G46" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>3200</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
-        <v>200</v>
+      <c r="K46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L46" s="3">
         <v>200</v>
       </c>
       <c r="M46" s="3">
+        <v>200</v>
+      </c>
+      <c r="N46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>297900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>293700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>7600</v>
       </c>
       <c r="E48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
+      <c r="G48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>500</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -1984,13 +2093,16 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>148000</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -2019,8 +2131,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2169,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,31 +2207,34 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2122,10 +2243,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2283,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>4</v>
+      <c r="D54" s="3">
+        <v>837800</v>
       </c>
       <c r="E54" s="3">
+        <v>356500</v>
+      </c>
+      <c r="F54" s="3">
         <v>274400</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
+      <c r="G54" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I54" s="3">
+        <v>3700</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>298100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>294000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2339,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,34 +2355,35 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>1500</v>
       </c>
       <c r="E57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+      <c r="G57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>400</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2259,133 +2391,145 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>5500</v>
       </c>
       <c r="E58" s="3">
-        <v>50200</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>50300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>42000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>41900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>26900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
-        <v>12700</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+        <v>3900</v>
+      </c>
+      <c r="F59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>21700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>7600</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>11400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>14400</v>
       </c>
       <c r="E60" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F60" s="3">
         <v>64000</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
+      <c r="G60" s="3">
+        <v>65300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>57500</v>
+      </c>
+      <c r="I60" s="3">
+        <v>34900</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>14800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2399,25 +2543,28 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
-        <v>200</v>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H62" s="3">
+        <v>600</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2425,8 +2572,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>10100</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>10100</v>
@@ -2434,8 +2581,11 @@
       <c r="M62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2619,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2657,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2695,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>21200</v>
       </c>
       <c r="E66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F66" s="3">
         <v>64200</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
+      <c r="G66" s="3">
+        <v>70100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>60500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>35200</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>24900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2751,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2787,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2825,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2863,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2901,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
+      <c r="D72" s="3">
+        <v>-2907500</v>
       </c>
       <c r="E72" s="3">
+        <v>-2888300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
+      <c r="G72" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-31600</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-24000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-16300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2977,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3015,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3053,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>4</v>
+      <c r="D76" s="3">
+        <v>816500</v>
       </c>
       <c r="E76" s="3">
+        <v>341700</v>
+      </c>
+      <c r="F76" s="3">
         <v>210300</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="G76" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>273200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>277000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3129,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-19200</v>
       </c>
       <c r="E81" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-327600</v>
       </c>
-      <c r="F81" s="3">
-        <v>-58200</v>
-      </c>
       <c r="G81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,34 +3228,35 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3064,8 +3264,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3302,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3340,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3378,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3416,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3454,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
+      <c r="D89" s="3">
+        <v>-21900</v>
       </c>
       <c r="E89" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-9300</v>
       </c>
-      <c r="F89" s="3">
-        <v>-9700</v>
-      </c>
       <c r="G89" s="3">
+        <v>700</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,19 +3510,20 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3312,8 +3534,8 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3324,8 +3546,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3584,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,28 +3622,31 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-310600</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-2100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
@@ -3429,8 +3660,11 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,31 +3678,32 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3479,8 +3714,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3752,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3790,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,66 +3828,72 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>360700</v>
       </c>
       <c r="E100" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F100" s="3">
         <v>280500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3654,39 +3904,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>28200</v>
       </c>
       <c r="E102" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F102" s="3">
         <v>271200</v>
       </c>
-      <c r="F102" s="3">
-        <v>-7200</v>
-      </c>
       <c r="G102" s="3">
+        <v>700</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3800</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -731,7 +734,7 @@
         <v>1000</v>
       </c>
       <c r="E8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="3">
         <v>800</v>
@@ -740,19 +743,19 @@
         <v>800</v>
       </c>
       <c r="H8" s="3">
+        <v>800</v>
+      </c>
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -760,23 +763,26 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
@@ -786,8 +792,8 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -798,35 +804,38 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>700</v>
       </c>
       <c r="G10" s="3">
         <v>700</v>
       </c>
       <c r="H10" s="3">
+        <v>700</v>
+      </c>
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -836,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,35 +864,36 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>3900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2200</v>
       </c>
       <c r="I12" s="3">
         <v>2200</v>
       </c>
       <c r="J12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K12" s="3">
         <v>2800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
@@ -890,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,23 +944,26 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -957,8 +976,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -966,17 +985,20 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
@@ -992,11 +1014,11 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1004,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,84 +1042,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E17" s="3">
         <v>22100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5000</v>
       </c>
       <c r="J17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="K17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-98400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3800</v>
       </c>
       <c r="J18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="K18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,113 +1141,120 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
         <v>225900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-324300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-3500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3">
         <v>2800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1223,46 +1262,52 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-327600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1275,11 +1320,11 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
@@ -1290,17 +1335,20 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-327600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-327600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>-3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,84 +1631,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>-225900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-327600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>-3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-327600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>-3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,37 +1877,38 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E41" s="3">
         <v>372100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>344000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>233700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="L41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -1830,17 +1916,20 @@
       <c r="N41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>606500</v>
+      </c>
+      <c r="E42" s="3">
         <v>300700</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1868,8 +1957,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1883,22 +1975,22 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -1906,8 +1998,11 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1932,8 +2027,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1944,8 +2039,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1973,8 +2071,8 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>200</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
@@ -1982,46 +2080,52 @@
       <c r="N45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>784300</v>
+      </c>
+      <c r="E46" s="3">
         <v>682100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>353500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>274100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
-        <v>200</v>
+      <c r="L46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M46" s="3">
         <v>200</v>
       </c>
       <c r="N46" s="3">
+        <v>200</v>
+      </c>
+      <c r="O46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2046,49 +2150,52 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>297900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>293700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
       </c>
       <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2096,17 +2203,20 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E49" s="3">
         <v>148000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -2134,8 +2244,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,8 +2326,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2236,8 +2355,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2246,10 +2365,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>938300</v>
+      </c>
+      <c r="E54" s="3">
         <v>837800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>356500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>274400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>298100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>294000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,8 +2485,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2365,28 +2495,28 @@
         <v>1500</v>
       </c>
       <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
-        <v>1600</v>
-      </c>
       <c r="H57" s="3">
+        <v>900</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2394,146 +2524,158 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E58" s="3">
         <v>5500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>26900</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>11400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E60" s="3">
         <v>14400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>14800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2546,8 +2688,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2560,23 +2705,23 @@
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>10100</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>10100</v>
@@ -2584,8 +2729,11 @@
       <c r="N62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E66" s="3">
         <v>21200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35200</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>24900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2866,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2945200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2907500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2888300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-57600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-24000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>913600</v>
+      </c>
+      <c r="E76" s="3">
         <v>816500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>341700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>210300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-66800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-57600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-31600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-8600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>273200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>277000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-327600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>-3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,13 +3426,14 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -3255,11 +3453,11 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3267,8 +3465,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,22 +3730,23 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3534,11 +3754,11 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3549,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,22 +3851,25 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-305800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-310600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -3648,8 +3877,8 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
@@ -3663,8 +3892,11 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +3911,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3705,8 +3938,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3717,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,46 +4073,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E100" s="3">
         <v>360700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>93800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>280500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3895,8 +4143,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3907,42 +4155,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-201900</v>
+      </c>
+      <c r="E102" s="3">
         <v>28200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>70200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>271200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,88 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E8" s="3">
         <v>1000</v>
       </c>
       <c r="F8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="3">
         <v>800</v>
@@ -746,19 +750,19 @@
         <v>800</v>
       </c>
       <c r="I8" s="3">
+        <v>800</v>
+      </c>
+      <c r="J8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -766,26 +770,29 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
       <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
@@ -795,8 +802,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -807,38 +814,41 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>700</v>
       </c>
       <c r="H10" s="3">
         <v>700</v>
       </c>
       <c r="I10" s="3">
+        <v>700</v>
+      </c>
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -848,8 +858,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,38 +878,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2200</v>
       </c>
       <c r="J12" s="3">
         <v>2200</v>
       </c>
       <c r="K12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
@@ -906,8 +920,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,26 +964,29 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -979,8 +999,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -988,20 +1008,23 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
@@ -1017,11 +1040,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1029,8 +1052,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1069,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E17" s="3">
         <v>46400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>99100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5000</v>
       </c>
       <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="L17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-45400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-98400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-3800</v>
       </c>
       <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,90 +1175,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
         <v>225900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-43200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-324300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1235,29 +1275,29 @@
       <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>2800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1265,49 +1305,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-327600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1323,11 +1369,11 @@
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
@@ -1338,17 +1384,20 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1437,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-327600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-22800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-327600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-22800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1613,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1701,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>-225900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-327600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-22800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1833,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-327600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-22800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,40 +1964,41 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E41" s="3">
         <v>170200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>372100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>344000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>233700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="M41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -1919,20 +2006,23 @@
       <c r="O41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>612900</v>
+      </c>
+      <c r="E42" s="3">
         <v>606500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>300700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1960,8 +2050,11 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1978,22 +2071,22 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2001,8 +2094,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2030,8 +2126,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2042,8 +2138,11 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2074,8 +2173,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>200</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
@@ -2083,49 +2182,55 @@
       <c r="O45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>766900</v>
+      </c>
+      <c r="E46" s="3">
         <v>784300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>682100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>353500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>274100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
-        <v>200</v>
+      <c r="M46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N46" s="3">
         <v>200</v>
       </c>
       <c r="O46" s="3">
+        <v>200</v>
+      </c>
+      <c r="P46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2153,52 +2258,55 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>297900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>293700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>400</v>
       </c>
       <c r="I48" s="3">
         <v>400</v>
       </c>
       <c r="J48" s="3">
+        <v>400</v>
+      </c>
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2206,20 +2314,23 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E49" s="3">
         <v>146200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>148000</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -2247,8 +2358,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,8 +2446,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2358,8 +2478,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2368,10 +2488,13 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2534,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>918900</v>
+      </c>
+      <c r="E54" s="3">
         <v>938300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>837800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>356500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>274400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>298100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>294000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,40 +2616,41 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="E57" s="3">
         <v>1500</v>
       </c>
       <c r="F57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2527,158 +2658,170 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E58" s="3">
         <v>5900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>50300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>41900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>26900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>11400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>57500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34900</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>14800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2691,8 +2834,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2708,23 +2854,23 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>10100</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>10100</v>
@@ -2732,8 +2878,11 @@
       <c r="O62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3010,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E66" s="3">
         <v>24700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>64200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>70100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>24900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3248,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2976900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2945200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2907500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2888300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-66800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-57600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-31600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-24000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-16300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3424,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>891700</v>
+      </c>
+      <c r="E76" s="3">
         <v>913600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>816500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>341700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>210300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-66800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-57600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-31600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-8600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>273200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>277000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3512,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-327600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-22800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,17 +3625,18 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
@@ -3456,11 +3655,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3468,8 +3667,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +3887,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +3951,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3740,16 +3961,16 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -3757,11 +3978,11 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3772,8 +3993,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,25 +4081,28 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-305800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-310600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -3880,8 +4110,8 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
@@ -3895,8 +4125,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4145,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3941,8 +4175,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3953,8 +4187,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4319,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E100" s="3">
         <v>112300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>360700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>93800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>280500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4146,8 +4395,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4158,45 +4407,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-201900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>70200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>271200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1000</v>
       </c>
       <c r="F8" s="3">
         <v>1000</v>
       </c>
       <c r="G8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="3">
         <v>800</v>
@@ -753,19 +757,19 @@
         <v>800</v>
       </c>
       <c r="J8" s="3">
+        <v>800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -773,8 +777,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -782,20 +789,20 @@
         <v>300</v>
       </c>
       <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
@@ -805,8 +812,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -817,8 +824,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -826,32 +836,32 @@
         <v>500</v>
       </c>
       <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>700</v>
       </c>
       <c r="I10" s="3">
         <v>700</v>
       </c>
       <c r="J10" s="3">
+        <v>700</v>
+      </c>
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -861,8 +871,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,41 +892,42 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E12" s="3">
         <v>12600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2200</v>
       </c>
       <c r="K12" s="3">
         <v>2200</v>
       </c>
       <c r="L12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
@@ -923,8 +937,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,29 +984,32 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1002,8 +1022,8 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1011,8 +1031,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,14 +1043,14 @@
         <v>1800</v>
       </c>
       <c r="E15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F15" s="3">
         <v>2200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1043,11 +1066,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1055,8 +1078,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1096,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E17" s="3">
         <v>40400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>99100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5000</v>
       </c>
       <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="M17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-39500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-45400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-98400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-3800</v>
       </c>
       <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="M18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,101 +1209,108 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
         <v>225900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-43200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-324300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>4100</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1278,29 +1318,29 @@
       <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I22" s="3">
         <v>2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1308,57 +1348,63 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-327600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>300</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -1372,11 +1418,11 @@
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
@@ -1387,17 +1433,20 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1489,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-327600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-31700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-37600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-327600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1630,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1677,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1724,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1771,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>-225900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-31700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-327600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1912,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-31700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-327600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2032,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,43 +2051,44 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1343900</v>
+      </c>
+      <c r="E41" s="3">
         <v>146100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>170200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>372100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>344000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>233700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
+      <c r="N41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
@@ -2009,23 +2096,26 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>741700</v>
+      </c>
+      <c r="E42" s="3">
         <v>612900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>606500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>300700</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2053,13 +2143,16 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -2074,22 +2167,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2097,8 +2190,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2129,8 +2225,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2141,8 +2237,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2176,8 +2275,8 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
-        <v>200</v>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
@@ -2185,52 +2284,58 @@
       <c r="P45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3096700</v>
+      </c>
+      <c r="E46" s="3">
         <v>766900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>784300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>682100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>353500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>274100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3200</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
-        <v>200</v>
+      <c r="N46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O46" s="3">
         <v>200</v>
       </c>
       <c r="P46" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2261,55 +2366,58 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>297900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>293700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>400</v>
       </c>
       <c r="K48" s="3">
+        <v>400</v>
+      </c>
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2317,23 +2425,26 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E49" s="3">
         <v>144900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>146200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>148000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2361,8 +2472,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2519,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,8 +2566,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2481,8 +2601,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2491,10 +2611,13 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2660,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3247300</v>
+      </c>
+      <c r="E54" s="3">
         <v>918900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>938300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>837800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>356500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>274400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>298100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>294000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2728,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,43 +2747,44 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1500</v>
       </c>
       <c r="F57" s="3">
         <v>1500</v>
       </c>
       <c r="G57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2661,8 +2792,11 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2670,161 +2804,170 @@
         <v>5800</v>
       </c>
       <c r="E58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F58" s="3">
         <v>5900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>50300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>41900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>26900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>11400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E60" s="3">
         <v>20000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>57500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>14800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>941500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2837,8 +2980,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2857,23 +3003,23 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>10100</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>10100</v>
@@ -2881,8 +3027,11 @@
       <c r="P62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3074,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3121,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3168,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>965100</v>
+      </c>
+      <c r="E66" s="3">
         <v>27200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>64200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>70100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>60500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>24900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3236,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3281,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3328,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3375,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3422,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2996900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2976900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2945200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2907500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2888300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-66800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-57600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-24000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-16300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3516,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3563,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3610,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2281900</v>
+      </c>
+      <c r="E76" s="3">
         <v>891700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>913600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>816500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>341700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>210300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-66800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-57600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-31600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-8600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>273200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>277000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3704,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-31700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-327600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,20 +3824,21 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -3658,11 +3857,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -3670,8 +3869,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3916,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3963,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4010,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4057,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4104,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,28 +4172,29 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -3981,11 +4202,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3996,8 +4217,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4264,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,28 +4311,31 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-305800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-310600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -4113,8 +4343,8 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
@@ -4128,8 +4358,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4379,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4178,8 +4412,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4190,8 +4424,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4471,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4518,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,52 +4565,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2321200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>112300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>360700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>93800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>280500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
         <v>3300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4398,8 +4647,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4410,48 +4659,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2197800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-201900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>70200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>271200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,89 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -746,19 +749,19 @@
         <v>1000</v>
       </c>
       <c r="E8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1000</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
       </c>
       <c r="I8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="3">
         <v>800</v>
@@ -767,19 +770,19 @@
         <v>800</v>
       </c>
       <c r="L8" s="3">
+        <v>800</v>
+      </c>
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -787,35 +790,38 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
       </c>
       <c r="G9" s="3">
+        <v>300</v>
+      </c>
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
@@ -825,8 +831,8 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -837,8 +843,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -852,32 +861,32 @@
         <v>500</v>
       </c>
       <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>700</v>
       </c>
       <c r="K10" s="3">
         <v>700</v>
       </c>
       <c r="L10" s="3">
+        <v>700</v>
+      </c>
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -887,8 +896,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,47 +919,48 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E12" s="3">
         <v>8300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2200</v>
       </c>
       <c r="M12" s="3">
         <v>2200</v>
       </c>
       <c r="N12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
@@ -957,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,13 +1023,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>561200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1021,21 +1040,21 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1600</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1048,8 +1067,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1057,8 +1076,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1066,20 +1088,20 @@
         <v>1900</v>
       </c>
       <c r="E15" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="F15" s="3">
         <v>1800</v>
       </c>
       <c r="G15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H15" s="3">
         <v>2200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -1095,11 +1117,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1107,8 +1129,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E17" s="3">
         <v>58600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40400</v>
       </c>
-      <c r="G17" s="3">
-        <v>46400</v>
-      </c>
       <c r="H17" s="3">
+        <v>44700</v>
+      </c>
+      <c r="I17" s="3">
         <v>24700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5000</v>
       </c>
       <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="O17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-57700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-39500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-45400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-23700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-98400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3800</v>
       </c>
       <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="O18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,8 +1276,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1258,105 +1291,111 @@
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>225900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5700</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-55800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-41700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-37800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-43200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-22900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-324300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
@@ -1365,28 +1404,28 @@
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>-200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1394,70 +1433,76 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-605600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-327600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1470,11 +1515,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
@@ -1485,17 +1530,20 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-605800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-327600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-22800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-605500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-327600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,8 +1910,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1858,94 +1927,100 @@
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-225900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5700</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-605500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-327600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-605500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-327600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,49 +2224,50 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E41" s="3">
         <v>166100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1343900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>146100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>170200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>372100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>344000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
+      <c r="P41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q41" s="3">
         <v>0</v>
@@ -2189,29 +2275,32 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1137900</v>
+        <v>1027100</v>
       </c>
       <c r="E42" s="3">
+        <v>682900</v>
+      </c>
+      <c r="F42" s="3">
         <v>741700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>612900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>606500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>300700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2239,19 +2328,22 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>300</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2266,22 +2358,22 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2289,8 +2381,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2327,8 +2422,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2339,16 +2434,19 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="E45" s="3">
+        <v>455000</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -2380,8 +2478,8 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>200</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
@@ -2389,58 +2487,64 @@
       <c r="R45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1203200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1650200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3096700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>766900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>784300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>682100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>353500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>274100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3200</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P46" s="3">
-        <v>200</v>
+      <c r="P46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q46" s="3">
         <v>200</v>
       </c>
       <c r="R46" s="3">
+        <v>200</v>
+      </c>
+      <c r="S46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2477,61 +2581,64 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>297900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>293700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>400</v>
       </c>
       <c r="M48" s="3">
+        <v>400</v>
+      </c>
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2539,29 +2646,32 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E49" s="3">
         <v>142100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>143500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>144900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>146200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>148000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -2589,8 +2699,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,17 +2805,20 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1080200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1466700</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2727,8 +2846,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2737,10 +2856,13 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +2911,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2629700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3265300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3247300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>918900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>938300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>837800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>356500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>274400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>298100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>294000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,49 +3008,50 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1500</v>
       </c>
       <c r="H57" s="3">
         <v>1500</v>
       </c>
       <c r="I57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -2929,194 +3059,206 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>947500</v>
+      </c>
+      <c r="E58" s="3">
         <v>5500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5800</v>
       </c>
       <c r="F58" s="3">
         <v>5800</v>
       </c>
       <c r="G58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>41900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>13200</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
-        <v>1800</v>
-      </c>
       <c r="H59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>11400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>980100</v>
+      </c>
+      <c r="E60" s="3">
         <v>38600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>65300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>57500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>14800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E61" s="3">
         <v>948000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>941500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3129,8 +3271,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3155,23 +3300,23 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>10100</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>10100</v>
@@ -3179,8 +3324,11 @@
       <c r="R62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3483,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>982800</v>
+      </c>
+      <c r="E66" s="3">
         <v>987000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>965100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>70100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>24900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,58 +3769,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3657200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3051700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2996900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2976900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2945200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2907500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2888300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-66800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-57600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-16300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +3981,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1646700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2278100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2281900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>891700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>913600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>816500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>341700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>210300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-66800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-57600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-31600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-8600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3">
         <v>273200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>277000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-605500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-327600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,26 +4221,27 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -4062,11 +4260,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4074,8 +4272,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,58 +4537,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E89" s="3">
         <v>10100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,8 +4613,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4403,25 +4623,25 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4429,11 +4649,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4444,8 +4664,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,34 +4770,37 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-294200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1841100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-125700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-305800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-310600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2100</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4579,8 +4808,8 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
@@ -4594,8 +4823,11 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4652,8 +4885,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4664,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,58 +5056,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2321200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>112300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>360700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>93800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>280500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4902,8 +5150,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4914,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-336000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1842000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2197800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-201900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>70200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>271200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DJT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>DJT</t>
   </si>
@@ -656,115 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E8" s="3">
         <v>1000</v>
       </c>
       <c r="F8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1000</v>
       </c>
       <c r="I8" s="3">
         <v>1000</v>
       </c>
       <c r="J8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="K8" s="3">
         <v>800</v>
@@ -773,19 +777,19 @@
         <v>800</v>
       </c>
       <c r="M8" s="3">
+        <v>800</v>
+      </c>
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -793,38 +797,41 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
       <c r="M9" s="3">
         <v>0</v>
       </c>
@@ -834,8 +841,8 @@
       <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -846,13 +853,16 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>500</v>
+        <v>-600</v>
       </c>
       <c r="E10" s="3">
         <v>500</v>
@@ -864,32 +874,32 @@
         <v>500</v>
       </c>
       <c r="H10" s="3">
+        <v>500</v>
+      </c>
+      <c r="I10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>700</v>
       </c>
       <c r="L10" s="3">
         <v>700</v>
       </c>
       <c r="M10" s="3">
+        <v>700</v>
+      </c>
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -899,8 +909,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,50 +933,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E12" s="3">
         <v>8900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2200</v>
       </c>
       <c r="N12" s="3">
         <v>2200</v>
       </c>
       <c r="O12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
@@ -973,8 +987,11 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,38 +1043,41 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E14" s="3">
         <v>561200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1070,8 +1090,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1079,8 +1099,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1091,20 +1114,20 @@
         <v>1900</v>
       </c>
       <c r="F15" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="G15" s="3">
         <v>1800</v>
       </c>
       <c r="H15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1120,11 +1143,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1132,8 +1155,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1176,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E17" s="3">
         <v>30100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5000</v>
       </c>
       <c r="O17" s="3">
         <v>5000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="P17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-293500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-57700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-43500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-39500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-43700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-98400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-3800</v>
       </c>
       <c r="O18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="P18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1310,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1294,111 +1328,117 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>225900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5700</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-291600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-27200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-55800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-37800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-41600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-324300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E22" s="3">
         <v>11600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
@@ -1407,28 +1447,28 @@
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>-200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1436,76 +1476,82 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-605600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-54800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-37600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-327600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1518,11 +1564,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
@@ -1533,17 +1579,20 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1644,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-405900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-605800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-54800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-327600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-22800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-605500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-54800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-327600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1812,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1868,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1924,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1980,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1930,97 +2000,103 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-225900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5700</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-605500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-54800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-327600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2148,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-605500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-54800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-327600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2289,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,52 +2311,53 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249100</v>
+      </c>
+      <c r="E41" s="3">
         <v>134600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>166100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1343900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>146100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>170200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>372100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>344000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>233700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2400</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
@@ -2278,32 +2365,35 @@
       <c r="S41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>761500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1027100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>682900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>741700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>612900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>606500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>300700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2331,8 +2421,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2340,13 +2433,13 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>300</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -2361,22 +2454,22 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2384,8 +2477,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2425,8 +2521,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2437,20 +2533,23 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>455000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2481,8 +2580,8 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
-        <v>200</v>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
@@ -2490,61 +2589,67 @@
       <c r="S45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1051600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1203200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1650200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3096700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>766900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>784300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>682100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>353500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>274100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3200</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3">
-        <v>200</v>
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R46" s="3">
         <v>200</v>
       </c>
       <c r="S46" s="3">
+        <v>200</v>
+      </c>
+      <c r="T46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2584,64 +2689,67 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>297900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>293700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>293300</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>400</v>
       </c>
       <c r="M48" s="3">
         <v>400</v>
       </c>
       <c r="N48" s="3">
+        <v>400</v>
+      </c>
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2649,32 +2757,35 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E49" s="3">
         <v>140700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>142100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>143500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>144900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>146200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>148000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -2702,8 +2813,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2869,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,20 +2925,23 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>839700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1080200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1466700</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2849,8 +2969,8 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2859,10 +2979,13 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3037,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2236400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2629700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3265300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3247300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>918900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>938300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>837800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>356500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>274400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>298100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>294000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3117,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,52 +3139,53 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1500</v>
       </c>
       <c r="I57" s="3">
         <v>1500</v>
       </c>
       <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3062,206 +3193,218 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>959200</v>
+      </c>
+      <c r="E58" s="3">
         <v>947500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5800</v>
       </c>
       <c r="G58" s="3">
         <v>5800</v>
       </c>
       <c r="H58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I58" s="3">
         <v>5900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>42000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>3500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>13200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>11400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>980200</v>
+      </c>
+      <c r="E60" s="3">
         <v>980100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>57500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>14800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>948000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>941500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3417,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3303,23 +3449,23 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>10100</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>10100</v>
@@ -3327,8 +3473,11 @@
       <c r="S62" s="3">
         <v>10100</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3529,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3585,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3641,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>983500</v>
+      </c>
+      <c r="E66" s="3">
         <v>982800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>987000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>965100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>70100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>24900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3721,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3775,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3831,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3887,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3943,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4063100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3657200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3051700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2996900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2976900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2945200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2907500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2888300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2871900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-66800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-57600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-24000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4055,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4111,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4167,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1252800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1646700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2278100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2281900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>891700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>913600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>816500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>341700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>210300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-66800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-57600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-31600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-8600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>273200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>277000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>281400</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4279,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-605500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-54800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-327600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4420,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4231,20 +4430,20 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
+        <v>600</v>
+      </c>
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -4263,11 +4462,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4275,8 +4474,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4530,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4586,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4642,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4698,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4754,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E89" s="3">
         <v>12100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +4834,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4626,25 +4847,25 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4652,11 +4873,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4667,8 +4888,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4944,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,37 +5000,40 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-294200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1841100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-305800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-310600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -4811,8 +5041,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
@@ -4826,8 +5056,11 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5080,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4888,8 +5122,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4900,8 +5134,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5190,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5246,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5302,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-54000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2321200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>112300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>360700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>93800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>280500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5153,8 +5402,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5165,57 +5414,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-336000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1842000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2197800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-201900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>70200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>271200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
     </row>
